--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_352_Iceland.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_352_Iceland.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R17a79bf8378c4422"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R97707b644d8b4a78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Redaaf25c6f244bd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rc8b59f70dbb7446f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Re5a573d6cfc74d8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R528f69b21cc143b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rf62c53514cd34d63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rdef0a2365a6445fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Re0beaa68b6754926"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R4bd2002730fb4aa4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Raa9d51aa9ce2401d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R0fc8f2c5bda64d3e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ352CommercialTable" displayName="EEZ352CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ352CommercialTable" displayName="EEZ352CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ352FunctionalTable" displayName="EEZ352FunctionalTable" ref="A1:O23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O23"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ352FunctionalTable" displayName="EEZ352FunctionalTable" ref="A1:E23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E23"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ352ValidationTable" displayName="EEZ352ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ352ValidationTable" displayName="EEZ352ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -5987,7 +5941,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3efd5566ec0b465d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdce07b029df447d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5997,20 +5951,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6018,606 +5962,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>433382.09861495724</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.117699221359626</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1311.2914254431555</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>433382.09861495724</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1353.2587929526755</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$80,A2,'Species'!$U$2:$U$80))</x:f>
-        <x:v>586478135.6589744</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.117699221359626</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1311.2914254431555</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>568290229.8543534</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>18187905.80462098</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0320046075915863</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.03200460759158633</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>3140.7692368062</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.0597455593809917</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>114.74811483945297</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>3140.7692368062</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>115.3060803060979</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$80,A3,'Species'!$U$2:$U$80))</x:f>
-        <x:v>362149.7898420975</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.0597455593809917</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>114.74811483945297</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>360397.3490692589</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1752.4407728385995</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0048625240373281</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.004862524037328106</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>23256.1861862687</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.887645926531932</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>772.0508874801169</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>23256.1861862687</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1421.1238079824943</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$80,A4,'Species'!$U$2:$U$80))</x:f>
-        <x:v>33049919.87218006</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.887645926531932</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>772.0508874801169</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>17954959.184511583</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>15094960.687668476</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.8407126149687816</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.8407126149687817</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>0.19816714659999998</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.1600000000000006</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>144.54397707459296</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>0.19816714659999998</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$80,A5,'Species'!$U$2:$U$80))</x:f>
-        <x:v>28.643867495087864</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.1600000000000006</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>144.54397707459296</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>28.6438674950879</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>-3.552713678800501e-14</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>0.9999999999999988</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>-1.2403051645905537e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>381.6493709581</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.6729471566219645</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>470.92002306969323</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>381.6493709581</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>536.2394245449223</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$80,A6,'Species'!$U$2:$U$80))</x:f>
-        <x:v>204655.43906050312</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.6729471566219645</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>470.92002306969323</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>179726.33057612236</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>24929.108484380762</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1387059336518426</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.1387059336518426</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>147986.9182134658</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.282802244708445</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>191.77952768354635</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>147986.9182134658</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>200.90075228052223</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$80,A7,'Species'!$U$2:$U$80))</x:f>
-        <x:v>29730683.196761396</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.282802244708445</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>191.77952768354635</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>28380861.278322075</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1349821.9184393212</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0475609920785014</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.04756099207850133</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>78091.93695721733</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.616918611423268</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>413.92209684297546</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>78091.93695721733</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>416.8913453764694</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$80,A8,'Species'!$U$2:$U$80))</x:f>
-        <x:v>32555852.661148768</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.616918611423268</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>413.92209684297546</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>32323978.291860845</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>231874.36928792298</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0071734477481167</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.007173447748116722</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>4264.0743617229</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.281774994556395</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>191.32644170361885</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>4264.0743617229</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>193.85697841935058</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$80,A9,'Species'!$U$2:$U$80))</x:f>
-        <x:v>826620.5715190223</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.281774994556395</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>191.32644170361885</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>815830.1747880722</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>10790.396730950102</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0132262780470864</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.013226278047086353</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>63975.595815312605</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.962139319263626</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>916.5144557277432</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>63975.595815312605</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>959.5239980882228</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$80,A10,'Species'!$U$2:$U$80))</x:f>
-        <x:v>61386119.47678493</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.962139319263626</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>916.5144557277432</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>58634558.37852932</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>2751561.098255612</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.046927292953965</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.04692729295396506</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1410.6281464098001</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.0335234073421296</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1080.2478418597466</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1410.6281464098001</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1261.5443666054975</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$80,A11,'Species'!$U$2:$U$80))</x:f>
-        <x:v>1779569.9914784385</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.0335234073421296</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1080.2478418597466</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1523828.0108258012</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>255741.9806526373</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.167828638688722</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.16782863868872197</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra835a3541c364ec6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rade0e2cfcf0f4a25"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6627,20 +6177,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6648,1254 +6188,440 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>9.5945934739</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8100000000000005</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>645.6542290346563</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>9.5945934739</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>645.6542290346556</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$80,A2,'Species'!$U$2:$U$80))</x:f>
-        <x:v>6194.789852291842</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8100000000000005</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>645.6542290346563</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>6194.789852291849</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>-6.366462912410498e-12</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>-1.0277124913373997e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>598.1310135111</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.443988230758588</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2779.6379394404034</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>598.1310135111</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2799.55222200285</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$80,A3,'Species'!$U$2:$U$80))</x:f>
-        <x:v>1674499.0079238168</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.443988230758588</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2779.6379394404034</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1662587.6579113943</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>11911.35001242254</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0071643440607432</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.007164344060743257</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>5.6136873198</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.559133601751767</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>362.354452156031</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>5.6136873198</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>402.8529302118565</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$80,A4,'Species'!$U$2:$U$80))</x:f>
-        <x:v>2261.4903860745735</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.559133601751767</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>362.354452156031</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2034.1445933413872</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>227.34579273318627</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1117648142995267</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.11176481429952664</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>284645.5357227189</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.090101135243125</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1230.555299941727</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>284645.5357227189</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1230.7867303056269</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$80,A5,'Species'!$U$2:$U$80))</x:f>
-        <x:v>350337948.20825875</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.090101135243125</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1230.555299941727</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>350272072.588344</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>65875.61991477013</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0001880698607457</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.00018806986074562163</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>89377.86637904918</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.203705229102711</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1598.4727208377292</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>89377.86637904918</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1824.5403446322068</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$80,A6,'Species'!$U$2:$U$80))</x:f>
-        <x:v>163073523.12572172</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.203705229102711</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1598.4727208377292</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>142868081.25358975</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>20205441.872131974</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.141427264192535</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.14142726419253485</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>7434.379708215401</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.293321915040491</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>196.4816131172487</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>7434.379708215401</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>218.8056578873769</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$80,A7,'Species'!$U$2:$U$80))</x:f>
-        <x:v>1626684.3430406358</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.293321915040491</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>196.4816131172487</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1460718.9175963027</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>165965.42544433312</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.113619001879868</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.11361900187986804</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1332.3384558041998</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.029504215394866</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1070.2967714882775</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1332.3384558041998</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1257.0508340281788</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$80,A8,'Species'!$U$2:$U$80))</x:f>
-        <x:v>1674817.1670764852</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.029504215394866</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1070.2967714882775</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1425997.547776912</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>248819.61929957313</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.174488111629277</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.17448811162927702</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1377.6486039627</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.79</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>616.5950018614822</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1377.6486039627</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>616.5950018614822</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$80,A9,'Species'!$U$2:$U$80))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>849451.2435248493</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.79</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>616.5950018614822</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>849451.2435248493</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>73.6450902309</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.12095415476419</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1321.1561622030972</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>73.6450902309</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1382.5933489646477</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$80,A10,'Species'!$U$2:$U$80))</x:f>
-        <x:v>101821.21193714369</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.12095415476419</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1321.1561622030972</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>97296.66477455664</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>4524.547162587041</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0465025925921587</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.04650259259215865</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>143.19812899800002</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.87</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>74.13102413009177</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>143.19812899800002</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>74.13102413009177</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$80,A11,'Species'!$U$2:$U$80))</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>10615.423956134733</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.87</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>74.13102413009177</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>10615.423956134733</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>3302.4016446959</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.324063091351313</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>210.89344993544893</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>3302.4016446959</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>218.46398444795446</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$80,A12,'Species'!$U$2:$U$80))</x:f>
-        <x:v>721455.8215477443</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.324063091351313</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>210.89344993544893</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>696454.875922419</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>25000.945625325316</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0358974378522554</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.03589743785225545</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>9837.812755943101</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.6500000000000004</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>446.6835921509635</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>9837.812755943101</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>446.68359215096297</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$80,A13,'Species'!$U$2:$U$80))</x:f>
-        <x:v>4394389.540733229</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.6500000000000004</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>446.6835921509635</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>4394389.540733234</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>-4.6566128730773926e-9</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>0.9999999999999989</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>-1.0596723003078158e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>59948.7844958143</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.02065111100533</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>1048.6996208912603</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>59948.7844958143</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1085.357187444402</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$80,A14,'Species'!$U$2:$U$80))</x:f>
-        <x:v>65065844.13108758</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.02065111100533</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>1048.6996208912603</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>62868267.57365233</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>2197576.557435252</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0349552587060031</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.03495525870600324</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>210785.68737455734</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.5069320836559497</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>321.3158015539779</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>210785.68737455734</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>457.08872886103535</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$80,A15,'Species'!$U$2:$U$80))</x:f>
-        <x:v>96347761.904136</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.5069320836559497</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>321.3158015539779</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>67728772.09486209</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>28618989.809273914</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.4225529110315134</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.4225529110315135</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>66456.96466035741</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.63005049749867</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>426.62912212831844</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>66456.96466035741</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>426.66313291283234</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$80,A16,'Species'!$U$2:$U$80))</x:f>
-        <x:v>28354736.745865475</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.63005049749867</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>426.62912212831844</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>28352476.492360964</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>2260.253504510969</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0000797197911484</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.00007971979114840113</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>767.2767548175</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.088458878097842</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>122.59108197581014</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>767.2767548175</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>282.99319017904594</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$80,A17,'Species'!$U$2:$U$80))</x:f>
-        <x:v>217134.09659603</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.088458878097842</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>122.59108197581014</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>94061.28754796572</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>123072.80904806427</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>2.30843211119457</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>1.3084321111945696</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>2997.5711078082</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.0688099679010294</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>117.1682565991016</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>2997.5711078082</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>117.27306984320445</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$80,A18,'Species'!$U$2:$U$80))</x:f>
-        <x:v>351534.3658859628</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.0688099679010294</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>117.1682565991016</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>351220.1807337244</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>314.1851522384095</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.000894553244583</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.0008945532445830817</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small bathypelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>0.0813985401</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.01</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>102.32929922807536</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>0.0813985401</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>102.32929922807536</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$80,A19,'Species'!$U$2:$U$80))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>8.329455566621391</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.01</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>102.32929922807536</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>8.329455566621391</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>969.0724160192999</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.1500061676924753</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>141.2557605110307</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>969.0724160192999</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>141.2559172716314</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$80,A20,'Species'!$U$2:$U$80))</x:f>
-        <x:v>136887.2130274422</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.1500061676924753</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>141.2557605110307</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>136887.06111506815</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0.15191237404360436</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0000011097643036</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.000001109764303551713</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>15821.8064780533</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>4.1669079929253</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>1468.6151125239196</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>15821.8064780533</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>1986.0712853950738</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$80,A21,'Species'!$U$2:$U$80))</x:f>
-        <x:v>31423235.529139426</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>4.1669079929253</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>1468.6151125239196</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>23236144.101097926</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>8187091.428041499</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.3523429443551545</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.35234294435515456</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>4.62706</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>630.957344480193</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>4.62706</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$80,A22,'Species'!$U$2:$U$80))</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>2919.4774903505217</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.8</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
-        <x:v>2919.4774903505217</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>0.0175403747</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.84</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>691.8309709189363</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>0.0175403747</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>691.8309709189363</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$80,A23,'Species'!$U$2:$U$80))</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>12.134974458982946</x:v>
       </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.84</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>691.8309709189363</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
-        <x:v>12.134974458982946</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G23">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O23">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4ee79e5592c41f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41df14fdd1474230"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8070,7 +6796,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -8169,7 +6895,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>746373735.3016174</x:v>
+        <x:v>708464397.4967039</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8183,7 +6909,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>746373735.3016171</x:v>
+        <x:v>686516663.3818655</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8197,7 +6923,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>1.1920928955078125e-7</x:v>
+        <x:v>-37909337.8049134</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8211,7 +6937,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-1.1920928955078125e-7</x:v>
+        <x:v>-59857071.91975176</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8222,9 +6948,9 @@
         <x:v>EEZ_352</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -8236,47 +6962,19 @@
         <x:v>EEZ_352</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_352</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_352</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd76a5e59b82c49f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60f5b8e791bd42ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8323,7 +7021,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
